--- a/Bases_de_Dados/FootyStats/Austria Bundesliga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Austria Bundesliga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP121"/>
+  <dimension ref="A1:BP127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.9</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.6</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.6</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.1</v>
@@ -3094,7 +3094,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR12" t="n">
         <v>1.78</v>
@@ -3312,7 +3312,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR14" t="n">
         <v>0.73</v>
@@ -3966,7 +3966,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR16" t="n">
         <v>1.06</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ18" t="n">
         <v>0.4</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR20" t="n">
         <v>2.7</v>
@@ -5053,10 +5053,10 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR21" t="n">
         <v>0.6899999999999999</v>
@@ -5271,10 +5271,10 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR22" t="n">
         <v>1.46</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.6</v>
@@ -5707,10 +5707,10 @@
         <v>1.5</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR24" t="n">
         <v>1.38</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ25" t="n">
         <v>0.4</v>
@@ -6146,7 +6146,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR26" t="n">
         <v>1.28</v>
@@ -6361,10 +6361,10 @@
         <v>3</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR27" t="n">
         <v>1.09</v>
@@ -6579,7 +6579,7 @@
         <v>2</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.9</v>
@@ -6800,7 +6800,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR29" t="n">
         <v>1.47</v>
@@ -7233,7 +7233,7 @@
         <v>0.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.6</v>
@@ -7451,10 +7451,10 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR32" t="n">
         <v>1.35</v>
@@ -7669,7 +7669,7 @@
         <v>2</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.9</v>
@@ -7890,7 +7890,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR34" t="n">
         <v>1.52</v>
@@ -8108,7 +8108,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR35" t="n">
         <v>1.4</v>
@@ -8759,10 +8759,10 @@
         <v>3</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR38" t="n">
         <v>2.39</v>
@@ -8977,10 +8977,10 @@
         <v>2</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR39" t="n">
         <v>1.47</v>
@@ -9413,10 +9413,10 @@
         <v>0.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR41" t="n">
         <v>1.43</v>
@@ -9631,10 +9631,10 @@
         <v>3</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR42" t="n">
         <v>1.09</v>
@@ -10067,7 +10067,7 @@
         <v>1.33</v>
       </c>
       <c r="AP44" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ44" t="n">
         <v>0.9</v>
@@ -10285,10 +10285,10 @@
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR45" t="n">
         <v>1.4</v>
@@ -10506,7 +10506,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR46" t="n">
         <v>1.82</v>
@@ -11157,7 +11157,7 @@
         <v>0.25</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.4</v>
@@ -11378,7 +11378,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR50" t="n">
         <v>1.25</v>
@@ -11593,7 +11593,7 @@
         <v>1.67</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.1</v>
@@ -11814,7 +11814,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR52" t="n">
         <v>1.46</v>
@@ -12029,10 +12029,10 @@
         <v>3</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ53" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR53" t="n">
         <v>1.51</v>
@@ -12247,10 +12247,10 @@
         <v>2.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR54" t="n">
         <v>2.2</v>
@@ -12465,10 +12465,10 @@
         <v>1.67</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR55" t="n">
         <v>1.14</v>
@@ -12683,10 +12683,10 @@
         <v>1.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR56" t="n">
         <v>1.39</v>
@@ -13119,10 +13119,10 @@
         <v>3</v>
       </c>
       <c r="AP58" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ58" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR58" t="n">
         <v>1.09</v>
@@ -13337,7 +13337,7 @@
         <v>1</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ59" t="n">
         <v>0.9</v>
@@ -13558,7 +13558,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR60" t="n">
         <v>1.72</v>
@@ -13773,10 +13773,10 @@
         <v>1.57</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR61" t="n">
         <v>1.39</v>
@@ -14430,7 +14430,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR64" t="n">
         <v>1.4</v>
@@ -14863,7 +14863,7 @@
         <v>1.75</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.9</v>
@@ -15081,10 +15081,10 @@
         <v>0.6</v>
       </c>
       <c r="AP67" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR67" t="n">
         <v>1.27</v>
@@ -15517,7 +15517,7 @@
         <v>1</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.9</v>
@@ -15735,10 +15735,10 @@
         <v>1.8</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR70" t="n">
         <v>1.9</v>
@@ -15953,10 +15953,10 @@
         <v>0.5</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR71" t="n">
         <v>1.28</v>
@@ -16174,7 +16174,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ72" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR72" t="n">
         <v>1.64</v>
@@ -16607,10 +16607,10 @@
         <v>1.5</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR74" t="n">
         <v>1.23</v>
@@ -16825,7 +16825,7 @@
         <v>0.4</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.6</v>
@@ -17264,7 +17264,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR77" t="n">
         <v>1.42</v>
@@ -17697,7 +17697,7 @@
         <v>1.67</v>
       </c>
       <c r="AP79" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.6</v>
@@ -17915,7 +17915,7 @@
         <v>2.2</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.1</v>
@@ -18136,7 +18136,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR81" t="n">
         <v>1.13</v>
@@ -18354,7 +18354,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR82" t="n">
         <v>1.82</v>
@@ -18569,10 +18569,10 @@
         <v>0.6</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR83" t="n">
         <v>1.98</v>
@@ -19005,7 +19005,7 @@
         <v>0.57</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ85" t="n">
         <v>0.4</v>
@@ -19441,10 +19441,10 @@
         <v>1</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR87" t="n">
         <v>1.77</v>
@@ -19659,7 +19659,7 @@
         <v>1.83</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.9</v>
@@ -19880,7 +19880,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ89" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR89" t="n">
         <v>1.13</v>
@@ -20098,7 +20098,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR90" t="n">
         <v>1.62</v>
@@ -20316,7 +20316,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR91" t="n">
         <v>1.9</v>
@@ -20534,7 +20534,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR92" t="n">
         <v>1.5</v>
@@ -20749,7 +20749,7 @@
         <v>1.71</v>
       </c>
       <c r="AP93" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.9</v>
@@ -20970,7 +20970,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR94" t="n">
         <v>1.12</v>
@@ -21185,7 +21185,7 @@
         <v>1.86</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.6</v>
@@ -22060,7 +22060,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR99" t="n">
         <v>1.12</v>
@@ -22275,10 +22275,10 @@
         <v>1.25</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR100" t="n">
         <v>1.21</v>
@@ -22493,7 +22493,7 @@
         <v>1.57</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.1</v>
@@ -22711,10 +22711,10 @@
         <v>1.75</v>
       </c>
       <c r="AP102" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR102" t="n">
         <v>1.29</v>
@@ -22929,10 +22929,10 @@
         <v>2.63</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ103" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR103" t="n">
         <v>1.65</v>
@@ -23147,7 +23147,7 @@
         <v>1.63</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.6</v>
@@ -23368,7 +23368,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR105" t="n">
         <v>1.65</v>
@@ -23586,7 +23586,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR106" t="n">
         <v>1.52</v>
@@ -23801,7 +23801,7 @@
         <v>0.5</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.4</v>
@@ -24019,7 +24019,7 @@
         <v>0.63</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ108" t="n">
         <v>0.6</v>
@@ -24240,7 +24240,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR109" t="n">
         <v>1.77</v>
@@ -24458,7 +24458,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ110" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR110" t="n">
         <v>1.43</v>
@@ -24676,7 +24676,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR111" t="n">
         <v>1.5</v>
@@ -25109,7 +25109,7 @@
         <v>1.88</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ113" t="n">
         <v>1.9</v>
@@ -25327,7 +25327,7 @@
         <v>1.38</v>
       </c>
       <c r="AP114" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.1</v>
@@ -25545,10 +25545,10 @@
         <v>1.67</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR115" t="n">
         <v>1.55</v>
@@ -25981,7 +25981,7 @@
         <v>1.78</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.6</v>
@@ -26420,7 +26420,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR119" t="n">
         <v>1.42</v>
@@ -26932,6 +26932,1314 @@
       </c>
       <c r="BP121" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="n">
+        <v>8206726</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Austria Bundesliga</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>46082.54166666666</v>
+      </c>
+      <c r="F122" t="n">
+        <v>21</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Salzburg</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Hartberg</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R122" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S122" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T122" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U122" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V122" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="W122" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X122" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>32</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="n">
+        <v>8206687</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Austria Bundesliga</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>46082.54166666666</v>
+      </c>
+      <c r="F123" t="n">
+        <v>21</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Blau-Weiß Linz</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Wattens</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" t="n">
+        <v>3</v>
+      </c>
+      <c r="K123" t="n">
+        <v>4</v>
+      </c>
+      <c r="L123" t="n">
+        <v>2</v>
+      </c>
+      <c r="M123" t="n">
+        <v>3</v>
+      </c>
+      <c r="N123" t="n">
+        <v>5</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>['16', '50']</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>['15', '19', '45+1']</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R123" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S123" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="T123" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U123" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V123" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="W123" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X123" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="n">
+        <v>8206684</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Austria Bundesliga</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>46082.54166666666</v>
+      </c>
+      <c r="F124" t="n">
+        <v>21</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Grazer AK</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Ried</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>2</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>2</v>
+      </c>
+      <c r="L124" t="n">
+        <v>2</v>
+      </c>
+      <c r="M124" t="n">
+        <v>1</v>
+      </c>
+      <c r="N124" t="n">
+        <v>3</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>['7', '26']</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="R124" t="n">
+        <v>2</v>
+      </c>
+      <c r="S124" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T124" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U124" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="V124" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W124" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X124" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="n">
+        <v>8206685</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Austria Bundesliga</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>46082.54166666666</v>
+      </c>
+      <c r="F125" t="n">
+        <v>21</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Wolfsberger AC</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sturm Graz</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1</v>
+      </c>
+      <c r="L125" t="n">
+        <v>2</v>
+      </c>
+      <c r="M125" t="n">
+        <v>2</v>
+      </c>
+      <c r="N125" t="n">
+        <v>4</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>['19', '51']</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>['68', '73']</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R125" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S125" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T125" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U125" t="n">
+        <v>3</v>
+      </c>
+      <c r="V125" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="W125" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X125" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="n">
+        <v>8206686</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Austria Bundesliga</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>46082.54166666666</v>
+      </c>
+      <c r="F126" t="n">
+        <v>21</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Austria Wien</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1</v>
+      </c>
+      <c r="L126" t="n">
+        <v>2</v>
+      </c>
+      <c r="M126" t="n">
+        <v>2</v>
+      </c>
+      <c r="N126" t="n">
+        <v>4</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>['47', '87']</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>['23', '73']</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="R126" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S126" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T126" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U126" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V126" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="W126" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X126" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="n">
+        <v>8206688</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Austria Bundesliga</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>46082.54166666666</v>
+      </c>
+      <c r="F127" t="n">
+        <v>21</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Rheindorf Altach</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Rapid Wien</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>1</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1</v>
+      </c>
+      <c r="N127" t="n">
+        <v>2</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R127" t="n">
+        <v>2</v>
+      </c>
+      <c r="S127" t="n">
+        <v>3</v>
+      </c>
+      <c r="T127" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U127" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="V127" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="W127" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X127" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Austria Bundesliga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Austria Bundesliga_20252026.xlsx
@@ -27525,13 +27525,13 @@
         <v>5</v>
       </c>
       <c r="AV124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW124" t="n">
         <v>4</v>
       </c>
       <c r="AX124" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY124" t="n">
         <v>9</v>
